--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,241 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136931319</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björkhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555750</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7032957</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931319</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136931320</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björkhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555752</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7032951</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931320</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38733-2022 artfynd.xlsx
+++ b/artfynd/A 38733-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136931319</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136931320</v>
       </c>
       <c r="B4" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
